--- a/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T19:39:21+00:00</t>
+    <t>2024-11-14T19:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T19:54:42+00:00</t>
+    <t>2024-11-29T17:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T17:24:43+00:00</t>
+    <t>2024-11-29T17:24:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T17:24:50+00:00</t>
+    <t>2024-12-11T15:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T15:33:45+00:00</t>
+    <t>2024-12-11T16:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T16:17:48+00:00</t>
+    <t>2024-12-23T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
+++ b/branches/cpg-guidance/StructureDefinition-ext-radiation-level-score.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-23T15:55:45+00:00</t>
+    <t>2024-12-23T16:34:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
